--- a/data/input/patch/priority_grn_codes.xlsx
+++ b/data/input/patch/priority_grn_codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unicef-my.sharepoint.com/personal/cmanili_unicef_org/Documents/ARR/ARR/data/input/patch/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2ad4b7826eb0755/ECW/repositories/AnnualResultsReport/data/input/patch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{9813AA71-EBCC-4D79-9427-4EFC0D5BF47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300111E8-54E4-48AF-835D-6519000EF2D9}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{9813AA71-EBCC-4D79-9427-4EFC0D5BF47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28A34442-33E3-4ABB-8EF8-93FF985616F6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{27A7454E-9C30-4776-98A2-274E41379A05}"/>
+    <workbookView xWindow="28680" yWindow="-4830" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{27A7454E-9C30-4776-98A2-274E41379A05}"/>
   </bookViews>
   <sheets>
     <sheet name="LeadGRN" sheetId="1" r:id="rId1"/>
@@ -721,7 +721,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -986,9 +986,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1026,7 +1026,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1132,7 +1132,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1274,7 +1274,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1283,13 +1283,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06BC2A33-9B9B-4E60-B4AB-A7FEA7DF3AD2}">
   <dimension ref="A1:B82"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>45</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>52</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>54</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>55</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>43</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>39</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>41</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>48</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>46</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>44</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>35</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>23</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>25</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>33</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>19</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>21</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>27</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>29</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>15</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>13</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>9</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>3</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>5</v>
       </c>
@@ -1729,137 +1729,137 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B64" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="2:2">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="2:2">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="2:2">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="2:2">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="2:2">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="2:2">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="2:2">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="2:2">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="2:2">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="2:2">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="2:2">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="2:2">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="2:2">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="2:2">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="2:2">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="2:2">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="2:2">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="2:2">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="2" t="s">
         <v>82</v>
       </c>
@@ -1872,18 +1872,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A5E677-BC3E-41D9-B841-C0B8731276A3}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H53"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="51.140625" customWidth="1"/>
-    <col min="4" max="4" width="62.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.85546875" customWidth="1"/>
+    <col min="3" max="3" width="51.109375" customWidth="1"/>
+    <col min="4" max="4" width="62.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.15">
+    <row r="1" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>83</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="46.9">
+    <row r="2" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>91</v>
       </c>
@@ -1935,7 +1934,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.15">
+    <row r="3" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>97</v>
       </c>
@@ -1961,7 +1960,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="31.15">
+    <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>97</v>
       </c>
@@ -1987,7 +1986,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="31.15">
+    <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>97</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.9">
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>91</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="31.15">
+    <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>97</v>
       </c>
@@ -2065,7 +2064,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="31.15">
+    <row r="8" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>97</v>
       </c>
@@ -2091,7 +2090,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="31.15">
+    <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>97</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="31.15">
+    <row r="10" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
@@ -2143,7 +2142,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="33.950000000000003" customHeight="1">
+    <row r="11" spans="1:8" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>91</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="42" customHeight="1">
+    <row r="12" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>91</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="31.15">
+    <row r="13" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>97</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="31.15">
+    <row r="14" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>97</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="31.15">
+    <row r="15" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>91</v>
       </c>
@@ -2273,7 +2272,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="31.15">
+    <row r="16" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>91</v>
       </c>
@@ -2299,7 +2298,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28.9">
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>91</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="31.15">
+    <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>97</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="28.9">
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>91</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="31.15" hidden="1">
+    <row r="20" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>97</v>
       </c>
@@ -2400,7 +2399,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28.9">
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>91</v>
       </c>
@@ -2426,7 +2425,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="62.45">
+    <row r="22" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>91</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="31.15">
+    <row r="23" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>97</v>
       </c>
@@ -2478,7 +2477,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="31.15">
+    <row r="24" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>97</v>
       </c>
@@ -2504,7 +2503,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="46.9">
+    <row r="25" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>97</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="46.9">
+    <row r="26" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>97</v>
       </c>
@@ -2556,7 +2555,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="62.45">
+    <row r="27" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>97</v>
       </c>
@@ -2582,7 +2581,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="31.15">
+    <row r="28" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>91</v>
       </c>
@@ -2608,7 +2607,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="31.15">
+    <row r="29" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>91</v>
       </c>
@@ -2634,7 +2633,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="46.9">
+    <row r="30" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>97</v>
       </c>
@@ -2660,7 +2659,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="46.9">
+    <row r="31" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
@@ -2686,7 +2685,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="46.9">
+    <row r="32" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>97</v>
       </c>
@@ -2712,7 +2711,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="46.9">
+    <row r="33" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>97</v>
       </c>
@@ -2738,7 +2737,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="46.9">
+    <row r="34" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>97</v>
       </c>
@@ -2764,7 +2763,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="46.9">
+    <row r="35" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>97</v>
       </c>
@@ -2790,7 +2789,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="46.9">
+    <row r="36" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>97</v>
       </c>
@@ -2816,7 +2815,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="46.9">
+    <row r="37" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>97</v>
       </c>
@@ -2842,7 +2841,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="31.15">
+    <row r="38" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>97</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="43.15">
+    <row r="39" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>91</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="46.9">
+    <row r="40" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>97</v>
       </c>
@@ -2920,7 +2919,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="46.9">
+    <row r="41" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>97</v>
       </c>
@@ -2946,7 +2945,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="46.9">
+    <row r="42" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>97</v>
       </c>
@@ -2972,7 +2971,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.6">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>97</v>
       </c>
@@ -2998,7 +2997,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="31.15">
+    <row r="44" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>97</v>
       </c>
@@ -3024,7 +3023,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="31.15">
+    <row r="45" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>97</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="28.9">
+    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
         <v>91</v>
       </c>
@@ -3076,7 +3075,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="31.15">
+    <row r="47" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>97</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="31.15">
+    <row r="48" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>97</v>
       </c>
@@ -3128,7 +3127,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="31.15">
+    <row r="49" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>97</v>
       </c>
@@ -3154,7 +3153,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="31.15">
+    <row r="50" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>97</v>
       </c>
@@ -3180,7 +3179,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="31.15">
+    <row r="51" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>97</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="62.45">
+    <row r="52" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>91</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="28.9">
+    <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>91</v>
       </c>
@@ -3259,14 +3258,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H53" xr:uid="{65A5E677-BC3E-41D9-B841-C0B8731276A3}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="0"/>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H53" xr:uid="{65A5E677-BC3E-41D9-B841-C0B8731276A3}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E52">
     <sortCondition ref="E3:E52"/>
   </sortState>
@@ -3325,23 +3317,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ca283e0b-db31-4043-a2ef-b80661bf084a" xsi:nil="true"/>
-    <Date xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b" xsi:nil="true"/>
-    <_dlc_DocId xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">AYUN26JUV6DU-776324767-60698</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">
-      <Url>https://unicef.sharepoint.com/teams/UHF-ECW/_layouts/15/DocIdRedir.aspx?ID=AYUN26JUV6DU-776324767-60698</Url>
-      <Description>AYUN26JUV6DU-776324767-60698</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006C51014E07575D42821B7CE8106B5FF8" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d92c3d3315f45275ed8052f4a76a54d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b7d2a3e2-2ca2-4894-a2fe-716ab1871804" xmlns:ns3="b044368c-7fce-458d-b3b9-18ac4fe4c16b" xmlns:ns4="ca283e0b-db31-4043-a2ef-b80661bf084a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81e4e6443a7ce9196a764929b11a8f4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b7d2a3e2-2ca2-4894-a2fe-716ab1871804"/>
@@ -3632,77 +3666,67 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ca283e0b-db31-4043-a2ef-b80661bf084a" xsi:nil="true"/>
+    <Date xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b" xsi:nil="true"/>
+    <_dlc_DocId xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">AYUN26JUV6DU-776324767-60698</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">
+      <Url>https://unicef.sharepoint.com/teams/UHF-ECW/_layouts/15/DocIdRedir.aspx?ID=AYUN26JUV6DU-776324767-60698</Url>
+      <Description>AYUN26JUV6DU-776324767-60698</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2EB3A28-81F5-4B9E-B784-9EA1BE08C7F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17AC8B00-525D-480F-98BD-389BFC0417BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDC73CA-7615-46C8-9782-5B33133BAD99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{116E5FD2-DEFE-4559-AAB4-A129C268DF2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{116E5FD2-DEFE-4559-AAB4-A129C268DF2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDC73CA-7615-46C8-9782-5B33133BAD99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b7d2a3e2-2ca2-4894-a2fe-716ab1871804"/>
+    <ds:schemaRef ds:uri="b044368c-7fce-458d-b3b9-18ac4fe4c16b"/>
+    <ds:schemaRef ds:uri="ca283e0b-db31-4043-a2ef-b80661bf084a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17AC8B00-525D-480F-98BD-389BFC0417BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2EB3A28-81F5-4B9E-B784-9EA1BE08C7F3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b044368c-7fce-458d-b3b9-18ac4fe4c16b"/>
+    <ds:schemaRef ds:uri="ca283e0b-db31-4043-a2ef-b80661bf084a"/>
+    <ds:schemaRef ds:uri="b7d2a3e2-2ca2-4894-a2fe-716ab1871804"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/input/patch/priority_grn_codes.xlsx
+++ b/data/input/patch/priority_grn_codes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2ad4b7826eb0755/ECW/repositories/AnnualResultsReport/data/input/patch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{9813AA71-EBCC-4D79-9427-4EFC0D5BF47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28A34442-33E3-4ABB-8EF8-93FF985616F6}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{9813AA71-EBCC-4D79-9427-4EFC0D5BF47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6F6736-EE22-4C0C-8DC3-F1444F1A63FF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4830" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{27A7454E-9C30-4776-98A2-274E41379A05}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{27A7454E-9C30-4776-98A2-274E41379A05}"/>
   </bookViews>
   <sheets>
     <sheet name="LeadGRN" sheetId="1" r:id="rId1"/>
@@ -1285,7 +1285,7 @@
   <dimension ref="A1:B82"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1880,6 +1880,7 @@
     <col min="3" max="3" width="51.109375" customWidth="1"/>
     <col min="4" max="4" width="62.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.88671875" customWidth="1"/>
+    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -3317,65 +3318,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ca283e0b-db31-4043-a2ef-b80661bf084a" xsi:nil="true"/>
+    <Date xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b" xsi:nil="true"/>
+    <_dlc_DocId xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">AYUN26JUV6DU-776324767-60698</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">
+      <Url>https://unicef.sharepoint.com/teams/UHF-ECW/_layouts/15/DocIdRedir.aspx?ID=AYUN26JUV6DU-776324767-60698</Url>
+      <Description>AYUN26JUV6DU-776324767-60698</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006C51014E07575D42821B7CE8106B5FF8" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d92c3d3315f45275ed8052f4a76a54d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b7d2a3e2-2ca2-4894-a2fe-716ab1871804" xmlns:ns3="b044368c-7fce-458d-b3b9-18ac4fe4c16b" xmlns:ns4="ca283e0b-db31-4043-a2ef-b80661bf084a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81e4e6443a7ce9196a764929b11a8f4" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b7d2a3e2-2ca2-4894-a2fe-716ab1871804"/>
@@ -3666,40 +3625,78 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ca283e0b-db31-4043-a2ef-b80661bf084a" xsi:nil="true"/>
-    <Date xmlns="b044368c-7fce-458d-b3b9-18ac4fe4c16b" xsi:nil="true"/>
-    <_dlc_DocId xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">AYUN26JUV6DU-776324767-60698</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="b7d2a3e2-2ca2-4894-a2fe-716ab1871804">
-      <Url>https://unicef.sharepoint.com/teams/UHF-ECW/_layouts/15/DocIdRedir.aspx?ID=AYUN26JUV6DU-776324767-60698</Url>
-      <Description>AYUN26JUV6DU-776324767-60698</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17AC8B00-525D-480F-98BD-389BFC0417BF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2EB3A28-81F5-4B9E-B784-9EA1BE08C7F3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b044368c-7fce-458d-b3b9-18ac4fe4c16b"/>
+    <ds:schemaRef ds:uri="ca283e0b-db31-4043-a2ef-b80661bf084a"/>
+    <ds:schemaRef ds:uri="b7d2a3e2-2ca2-4894-a2fe-716ab1871804"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{116E5FD2-DEFE-4559-AAB4-A129C268DF2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FDC73CA-7615-46C8-9782-5B33133BAD99}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3719,14 +3716,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{116E5FD2-DEFE-4559-AAB4-A129C268DF2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2EB3A28-81F5-4B9E-B784-9EA1BE08C7F3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17AC8B00-525D-480F-98BD-389BFC0417BF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b044368c-7fce-458d-b3b9-18ac4fe4c16b"/>
-    <ds:schemaRef ds:uri="ca283e0b-db31-4043-a2ef-b80661bf084a"/>
-    <ds:schemaRef ds:uri="b7d2a3e2-2ca2-4894-a2fe-716ab1871804"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>